--- a/business_forms/023_customer_service_skills_assessment_form--business_forms.xlsx
+++ b/business_forms/023_customer_service_skills_assessment_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,20 +515,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>customer_service_representative_skills</t>
+          <t>customer_service_skills_definition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Customer Service Representative Skills</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is the definition of customer service skills?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please specify the definition of customer service skills.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -538,20 +542,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>customer_service_skills_assessment</t>
+          <t>key_customer_service_skills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Customer Service Skills Assessment</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Which of the following is a key skill for customer service representatives?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Choose one or more of the following options.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -561,43 +569,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>performance_evaluation</t>
+          <t>self_assessment</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Performance Evaluation</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How would you rate your customer service skills?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Rate your customer service skills on a scale of 1-5.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>customer_service_skills</t>
+          <t>essential_skills</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>customer service skills</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What skills do you think are essential for a customer service representative to have?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>List the essential skills for a customer service representative.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -607,20 +623,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>customer_service_skills</t>
+          <t>problem_solving_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>customer service skills</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Can you describe your experience with problem-solving in a customer service role?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please describe a situation where you had to solve a difficult customer problem.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>communication_skills</t>
+          <t>adaptability_rating</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Communication Skills</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you rate your ability to adapt to changing situations?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rate your ability to adapt on a scale of 1-5.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -653,23 +677,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>problem_solving</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Problem Solving</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What is your availability for customer service skills assessment?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Specify your availability.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>adaptability</t>
+          <t>years_in_customer_service</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How many years have you been working in customer service?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Specify the number of years you have been working in customer service.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>customer_service_skills</t>
+          <t>customer_service_certification</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>customer service skills</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Do you have any certifications or training related to customer service?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Specify the certifications or training you have received.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,38 +763,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customer_service_skills</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>customer service skills</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How would you rate your communication skills?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rate your communication skills on a scale of 1-5.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>customer_service_skills_assessment</t>
+          <t>problem_solving_example</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>customer service skills assessment</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Can you give an example of a time when you had to solve a difficult customer problem?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Describe the situation and how you handled it.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,110 +817,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>communication_skills</t>
+          <t>pressure_rating</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>communication skills</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>How would you rate your ability to work under pressure?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rate your ability to work under pressure on a scale of 1-5.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>adaptability</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>customer_service</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>customer service</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>customer_service</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>customer service</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -891,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -919,272 +875,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>customer_service_representative_skills_choices</t>
+          <t>key_customer_service_skills_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>communication_skills</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Communication skills</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_service_representative_skills_choices</t>
+          <t>key_customer_service_skills_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>problem-solving_skills</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Problem-solving skills</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_service_skills_assessment_choices</t>
+          <t>key_customer_service_skills_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>adaptability</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Adaptability</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_service_skills_assessment_choices</t>
+          <t>key_customer_service_skills_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>customer_service_skills</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Customer service skills</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_service_skills_choices</t>
+          <t>key_customer_service_skills_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>customer_service_skills_choices</t>
+          <t>customer_service_certification_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>customer_service_skills_choices</t>
+          <t>customer_service_certification_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>customer_service_skills_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>customer_service_skills_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>customer_service_skills_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>customer_service_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>customer_service_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>customer_service_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>customer_service_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>communication_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>communication_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
